--- a/products-storage/07-uderzhaniya-shtrafy-zachety/05-reestr-uderzhaniy.xlsx
+++ b/products-storage/07-uderzhaniya-shtrafy-zachety/05-reestr-uderzhaniy.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="E5" s="2">
-        <f>СУММ(E2:E20)</f>
+        <f>SUM(E2:E20)</f>
         <v/>
       </c>
       <c r="F5" s="2" t="inlineStr"/>

--- a/products-storage/07-uderzhaniya-shtrafy-zachety/05-reestr-uderzhaniy.xlsx
+++ b/products-storage/07-uderzhaniya-shtrafy-zachety/05-reestr-uderzhaniy.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр удержаний и штрафов по объекту" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр удержаний и штрафов" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -562,21 +562,181 @@
       <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>ИТОГО:</t>
         </is>
       </c>
-      <c r="E5" s="2">
+      <c r="E21" s="2">
         <f>SUM(E2:E20)</f>
         <v/>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/products-storage/07-uderzhaniya-shtrafy-zachety/05-reestr-uderzhaniy.xlsx
+++ b/products-storage/07-uderzhaniya-shtrafy-zachety/05-reestr-uderzhaniy.xlsx
@@ -9,14 +9,19 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр удержаний и штрафов" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Реестр удержаний и штрафов'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Реестр удержаний и штрафов'!$A$1:$M$21</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -63,12 +68,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -434,19 +445,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,10 +498,35 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Дата отправки</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Способ отправки</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Подтверждение отправки</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Срок ответа</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Основание срока</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Ответ</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Результат</t>
         </is>
@@ -495,14 +536,14 @@
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Удержание</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -510,25 +551,30 @@
           <t>Оспаривается</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Претензия направлена</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Штраф</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -536,21 +582,26 @@
           <t>Оспаривается</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Зачет</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -558,168 +609,253 @@
           <t>Оспаривается</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" s="3" t="n"/>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
+      <c r="E5" s="4" t="n"/>
       <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
+      <c r="G5" s="3" t="n"/>
       <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" s="3" t="n"/>
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
+      <c r="E6" s="4" t="n"/>
       <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
+      <c r="G6" s="3" t="n"/>
       <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
+      <c r="B7" s="3" t="n"/>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
+      <c r="E7" s="4" t="n"/>
       <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
+      <c r="G7" s="3" t="n"/>
       <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
+      <c r="B8" s="3" t="n"/>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
+      <c r="E8" s="4" t="n"/>
       <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
+      <c r="G8" s="3" t="n"/>
       <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="n"/>
+      <c r="B9" s="3" t="n"/>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
+      <c r="E9" s="4" t="n"/>
       <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
+      <c r="G9" s="3" t="n"/>
       <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
-      <c r="B10" s="2" t="n"/>
+      <c r="B10" s="3" t="n"/>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
+      <c r="E10" s="4" t="n"/>
       <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
+      <c r="G10" s="3" t="n"/>
       <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
+      <c r="B11" s="3" t="n"/>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
+      <c r="E11" s="4" t="n"/>
       <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
+      <c r="G11" s="3" t="n"/>
       <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="n"/>
+      <c r="B12" s="3" t="n"/>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
+      <c r="E12" s="4" t="n"/>
       <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
+      <c r="G12" s="3" t="n"/>
       <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
-      <c r="B13" s="2" t="n"/>
+      <c r="B13" s="3" t="n"/>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
+      <c r="E13" s="4" t="n"/>
       <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
+      <c r="G13" s="3" t="n"/>
       <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
-      <c r="B14" s="2" t="n"/>
+      <c r="B14" s="3" t="n"/>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
+      <c r="E14" s="4" t="n"/>
       <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
+      <c r="G14" s="3" t="n"/>
       <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="3" t="n"/>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
+      <c r="E15" s="4" t="n"/>
       <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
+      <c r="G15" s="3" t="n"/>
       <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
-      <c r="B16" s="2" t="n"/>
+      <c r="B16" s="3" t="n"/>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
+      <c r="E16" s="4" t="n"/>
       <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
+      <c r="G16" s="3" t="n"/>
       <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
-      <c r="B17" s="2" t="n"/>
+      <c r="B17" s="3" t="n"/>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
+      <c r="E17" s="4" t="n"/>
       <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
+      <c r="G17" s="3" t="n"/>
       <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
-      <c r="B18" s="2" t="n"/>
+      <c r="B18" s="3" t="n"/>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
+      <c r="E18" s="4" t="n"/>
       <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
+      <c r="G18" s="3" t="n"/>
       <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="B19" s="3" t="n"/>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
+      <c r="E19" s="4" t="n"/>
       <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
+      <c r="G19" s="3" t="n"/>
       <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="B20" s="3" t="n"/>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
+      <c r="E20" s="4" t="n"/>
       <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
+      <c r="G20" s="3" t="n"/>
       <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr"/>
@@ -730,15 +866,21 @@
           <t>ИТОГО:</t>
         </is>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="4">
         <f>SUM(E2:E20)</f>
         <v/>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/products-storage/07-uderzhaniya-shtrafy-zachety/05-reestr-uderzhaniy.xlsx
+++ b/products-storage/07-uderzhaniya-shtrafy-zachety/05-reestr-uderzhaniy.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Реестр удержаний и штрафов'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Реестр удержаний и штрафов'!$A$1:$M$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Реестр удержаний и штрафов'!$A$1:$M$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -68,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -80,6 +80,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -863,7 +866,7 @@
       <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>ИТОГО:</t>
+          <t>Сумма записей (не размер требования):</t>
         </is>
       </c>
       <c r="E21" s="4">
@@ -879,7 +882,17 @@
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr"/>
     </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Одна и та же сумма может стоять в реестре несколько раз — например, штраф, удержанный из оплаты, и зачёт этого же штрафа. Итог складывает строки и размером требования не является.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A22:M22"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/products-storage/07-uderzhaniya-shtrafy-zachety/05-reestr-uderzhaniy.xlsx
+++ b/products-storage/07-uderzhaniya-shtrafy-zachety/05-reestr-uderzhaniy.xlsx
@@ -557,7 +557,7 @@
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
@@ -615,7 +615,7 @@
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
@@ -630,7 +630,7 @@
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
+      <c r="J5" s="3" t="n"/>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
@@ -645,7 +645,7 @@
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
+      <c r="J6" s="3" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
@@ -660,7 +660,7 @@
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
+      <c r="J7" s="3" t="n"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
@@ -675,7 +675,7 @@
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
+      <c r="J8" s="3" t="n"/>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
@@ -690,7 +690,7 @@
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
+      <c r="J9" s="3" t="n"/>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
@@ -705,7 +705,7 @@
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
+      <c r="J10" s="3" t="n"/>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
@@ -720,7 +720,7 @@
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
+      <c r="J11" s="3" t="n"/>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
@@ -735,7 +735,7 @@
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="n"/>
+      <c r="J12" s="3" t="n"/>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
@@ -750,7 +750,7 @@
       <c r="G13" s="3" t="n"/>
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
+      <c r="J13" s="3" t="n"/>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n"/>
@@ -765,7 +765,7 @@
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
+      <c r="J14" s="3" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
@@ -780,7 +780,7 @@
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
+      <c r="J15" s="3" t="n"/>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
@@ -795,7 +795,7 @@
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
+      <c r="J16" s="3" t="n"/>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
@@ -810,7 +810,7 @@
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
+      <c r="J17" s="3" t="n"/>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
@@ -825,7 +825,7 @@
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
+      <c r="J18" s="3" t="n"/>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
@@ -840,7 +840,7 @@
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
+      <c r="J19" s="3" t="n"/>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
@@ -855,7 +855,7 @@
       <c r="G20" s="3" t="n"/>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
-      <c r="J20" s="2" t="n"/>
+      <c r="J20" s="3" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
